--- a/stories/arbres/TREE-DIF-045.xlsx
+++ b/stories/arbres/TREE-DIF-045.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est avec papa, à l'école. Noé a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé écoute papa. Noé entend les mots : attendre, tendre un jouet, pas forcer la parole.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Noé respire. Noé retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Noé respire. Noé retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Noé respire. Noé retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. La lumière est claire. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-045.xlsx
+++ b/stories/arbres/TREE-DIF-045.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Noé est avec papa, à l'école. Noé a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé écoute papa. Noé entend les mots : attendre, tendre un jouet, pas forcer la parole.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Noé respire. Noé retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Noé a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Noé rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Noé rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Noé rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Noé a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Noé rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Noé rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Noé rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Noé a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Noé rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Noé rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Noé rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Noé respire. Noé retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Noé a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Noé rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Noé rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Noé rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Noé a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Noé rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Noé rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Noé rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Noé a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Noé rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Noé rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Noé rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Noé respire. Noé retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Noé a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Noé rejoint le matin. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Noé rejoint après la sieste. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Noé rejoint le soir. La lumière est claire. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Noé a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Noé rejoint le matin. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Noé rejoint après la sieste. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Noé rejoint le soir. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Noé a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Noé répète tout bas : attendre, tendre un jouet, pas forcer la parole. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Noé rejoint le matin. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Noé rejoint après la sieste. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Noé rejoint le soir. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Noé a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Noé a entendu : attendre, tendre un jouet, pas forcer la parole. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-045.xlsx
+++ b/stories/arbres/TREE-DIF-045.xlsx
@@ -4267,12 +4267,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse, puis s'arrête. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Le bleu garde une goutte, tout au fond. Toc. Une bulle se tait, puis l'autre. L'évier redevient calme, autour du bac.</t>
+          <t>Le bleu rejoint le bac, encore mouillé. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Le bleu garde une goutte, tout au fond. Toc. Une bulle se tait, puis l'autre. L'évier reste calme, derrière eux.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse, puis s'arrête. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Le bleu garde une goutte, tout au fond. Toc. Une bulle se tait, puis l'autre. L'évier redevient calme, autour du bac.</t>
+          <t>Le bleu rejoint le bac, encore mouillé. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Le bleu garde une goutte, tout au fond. Toc. Une bulle se tait, puis l'autre. L'évier reste calme, derrière eux.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4407,14 +4407,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|Une goutte glisse, puis s'arrête.
+          <t>narrateur|Le bleu rejoint le bac, encore mouillé.
 copine|On a attendu l'eau.
 papa|Le savon n'a plus pris vos bras.
 maman|Rentrez le torchon, après le bac.
 narrateur|Le bleu garde une goutte, tout au fond.
 enfant-m|Toc.
 narrateur|Une bulle se tait, puis l'autre.
-narrateur|L'évier redevient calme, autour du bac.</t>
+narrateur|L'évier reste calme, derrière eux.</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient le galet, tout net. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Le bleu garde une goutte, tout au fond. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. L'eau sent encore le savon tiède.</t>
+          <t>Le filet pose le galet au fond du bac. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Le bleu garde une goutte, tout au fond. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient le galet, tout net. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Le bleu garde une goutte, tout au fond. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. L'eau sent encore le savon tiède.</t>
+          <t>Le filet pose le galet au fond du bac. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Le bleu garde une goutte, tout au fond. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4755,14 +4755,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|Le filet tient le galet, tout net.
+          <t>narrateur|Le filet pose le galet au fond du bac.
 copine|On tenait, tous les deux.
 papa|Je remporte l'épuisette, tout à l'heure.
 maman|Le poisson vous attend.
 narrateur|Le bleu garde une goutte, tout au fond.
 narrateur|Aniss essuie une main sur son pantalon.
 narrateur|Un grain de craie reste sur le filet.
-narrateur|L'eau sent encore le savon tiède.</t>
+narrateur|Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Les mains d'Aniss laissent le bleu descendre. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Le bleu garde une goutte, tout au fond. Aniss pose un doigt sur le robinet. Il bouge, tout petit. Un rai de soleil barre encore l'évier.</t>
+          <t>Les mains d'Aniss laissent le bleu au fond du bac. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Le bleu garde une goutte, tout au fond. Aniss pose un doigt sur le verre. Une bulle bouge, toute petite. Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Les mains d'Aniss laissent le bleu descendre. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Le bleu garde une goutte, tout au fond. Aniss pose un doigt sur le robinet. Il bouge, tout petit. Un rai de soleil barre encore l'évier.</t>
+          <t>Les mains d'Aniss laissent le bleu au fond du bac. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Le bleu garde une goutte, tout au fond. Aniss pose un doigt sur le verre. Une bulle bouge, toute petite. Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5103,14 +5103,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|Les mains d'Aniss laissent le bleu descendre.
+          <t>narrateur|Les mains d'Aniss laissent le bleu au fond du bac.
 copine|C'était plus facile, là.
 papa|Tes bras ont guidé le galet.
 maman|Le fond gardera son ombre.
 narrateur|Le bleu garde une goutte, tout au fond.
-narrateur|Aniss pose un doigt sur le robinet.
-narrateur|Il bouge, tout petit.
-narrateur|Un rai de soleil barre encore l'évier.</t>
+narrateur|Aniss pose un doigt sur le verre.
+narrateur|Une bulle bouge, toute petite.
+narrateur|Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9240,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse, puis s'arrête. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. L'épuisette sent encore l'eau tiède. Toc. Une bulle se tait, puis l'autre. L'évier redevient calme, autour du bac.</t>
+          <t>Le bleu rejoint le bac, encore mouillé. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. L'épuisette sent encore l'eau tiède. Toc. Une bulle se tait, puis l'autre. L'évier reste calme, derrière eux.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse, puis s'arrête. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. L'épuisette sent encore l'eau tiède. Toc. Une bulle se tait, puis l'autre. L'évier redevient calme, autour du bac.</t>
+          <t>Le bleu rejoint le bac, encore mouillé. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. L'épuisette sent encore l'eau tiède. Toc. Une bulle se tait, puis l'autre. L'évier reste calme, derrière eux.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9380,14 +9380,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|Une goutte glisse, puis s'arrête.
+          <t>narrateur|Le bleu rejoint le bac, encore mouillé.
 copine|On a attendu l'eau.
 papa|Le savon n'a plus pris vos bras.
 maman|Rentrez le torchon, après le bac.
 narrateur|L'épuisette sent encore l'eau tiède.
 enfant-m|Toc.
 narrateur|Une bulle se tait, puis l'autre.
-narrateur|L'évier redevient calme, autour du bac.</t>
+narrateur|L'évier reste calme, derrière eux.</t>
         </is>
       </c>
     </row>
@@ -9588,12 +9588,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient le galet, tout net. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. L'épuisette sent encore l'eau tiède. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. L'eau sent encore le savon tiède.</t>
+          <t>Le filet pose le galet au fond du bac. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. L'épuisette sent encore l'eau tiède. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient le galet, tout net. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. L'épuisette sent encore l'eau tiède. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. L'eau sent encore le savon tiède.</t>
+          <t>Le filet pose le galet au fond du bac. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. L'épuisette sent encore l'eau tiède. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -9728,14 +9728,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|Le filet tient le galet, tout net.
+          <t>narrateur|Le filet pose le galet au fond du bac.
 copine|On tenait, tous les deux.
 papa|Je remporte l'épuisette, tout à l'heure.
 maman|Le poisson vous attend.
 narrateur|L'épuisette sent encore l'eau tiède.
 narrateur|Aniss essuie une main sur son pantalon.
 narrateur|Un grain de craie reste sur le filet.
-narrateur|L'eau sent encore le savon tiède.</t>
+narrateur|Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
     </row>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Les mains d'Aniss laissent le bleu descendre. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. L'épuisette sent encore l'eau tiède. Aniss pose un doigt sur le robinet. Il bouge, tout petit. Un rai de soleil barre encore l'évier.</t>
+          <t>Les mains d'Aniss laissent le bleu au fond du bac. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. L'épuisette sent encore l'eau tiède. Aniss pose un doigt sur le verre. Une bulle bouge, toute petite. Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Les mains d'Aniss laissent le bleu descendre. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. L'épuisette sent encore l'eau tiède. Aniss pose un doigt sur le robinet. Il bouge, tout petit. Un rai de soleil barre encore l'évier.</t>
+          <t>Les mains d'Aniss laissent le bleu au fond du bac. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. L'épuisette sent encore l'eau tiède. Aniss pose un doigt sur le verre. Une bulle bouge, toute petite. Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -10076,14 +10076,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|Les mains d'Aniss laissent le bleu descendre.
+          <t>narrateur|Les mains d'Aniss laissent le bleu au fond du bac.
 copine|C'était plus facile, là.
 papa|Tes bras ont guidé le galet.
 maman|Le fond gardera son ombre.
 narrateur|L'épuisette sent encore l'eau tiède.
-narrateur|Aniss pose un doigt sur le robinet.
-narrateur|Il bouge, tout petit.
-narrateur|Un rai de soleil barre encore l'évier.</t>
+narrateur|Aniss pose un doigt sur le verre.
+narrateur|Une bulle bouge, toute petite.
+narrateur|Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
     </row>
@@ -14213,12 +14213,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse, puis s'arrête. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Un carreau de torchon reste un peu humide. Toc. Une bulle se tait, puis l'autre. L'évier redevient calme, autour du bac.</t>
+          <t>Le bleu rejoint le bac, encore mouillé. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Un carreau de torchon reste un peu humide. Toc. Une bulle se tait, puis l'autre. L'évier reste calme, derrière eux.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse, puis s'arrête. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Un carreau de torchon reste un peu humide. Toc. Une bulle se tait, puis l'autre. L'évier redevient calme, autour du bac.</t>
+          <t>Le bleu rejoint le bac, encore mouillé. On a attendu l'eau. Le savon n'a plus pris vos bras. Rentrez le torchon, après le bac. Un carreau de torchon reste un peu humide. Toc. Une bulle se tait, puis l'autre. L'évier reste calme, derrière eux.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -14353,14 +14353,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|Une goutte glisse, puis s'arrête.
+          <t>narrateur|Le bleu rejoint le bac, encore mouillé.
 copine|On a attendu l'eau.
 papa|Le savon n'a plus pris vos bras.
 maman|Rentrez le torchon, après le bac.
 narrateur|Un carreau de torchon reste un peu humide.
 enfant-m|Toc.
 narrateur|Une bulle se tait, puis l'autre.
-narrateur|L'évier redevient calme, autour du bac.</t>
+narrateur|L'évier reste calme, derrière eux.</t>
         </is>
       </c>
     </row>
@@ -14561,12 +14561,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient le galet, tout net. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Un carreau de torchon reste un peu humide. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. L'eau sent encore le savon tiède.</t>
+          <t>Le filet pose le galet au fond du bac. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Un carreau de torchon reste un peu humide. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient le galet, tout net. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Un carreau de torchon reste un peu humide. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. L'eau sent encore le savon tiède.</t>
+          <t>Le filet pose le galet au fond du bac. On tenait, tous les deux. Je remporte l'épuisette, tout à l'heure. Le poisson vous attend. Un carreau de torchon reste un peu humide. Aniss essuie une main sur son pantalon. Un grain de craie reste sur le filet. Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -14701,14 +14701,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|Le filet tient le galet, tout net.
+          <t>narrateur|Le filet pose le galet au fond du bac.
 copine|On tenait, tous les deux.
 papa|Je remporte l'épuisette, tout à l'heure.
 maman|Le poisson vous attend.
 narrateur|Un carreau de torchon reste un peu humide.
 narrateur|Aniss essuie une main sur son pantalon.
 narrateur|Un grain de craie reste sur le filet.
-narrateur|L'eau sent encore le savon tiède.</t>
+narrateur|Le verre sent encore l'eau tiède.</t>
         </is>
       </c>
     </row>
@@ -14909,12 +14909,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Les mains d'Aniss laissent le bleu descendre. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Un carreau de torchon reste un peu humide. Aniss pose un doigt sur le robinet. Il bouge, tout petit. Un rai de soleil barre encore l'évier.</t>
+          <t>Les mains d'Aniss laissent le bleu au fond du bac. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Un carreau de torchon reste un peu humide. Aniss pose un doigt sur le verre. Une bulle bouge, toute petite. Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Les mains d'Aniss laissent le bleu descendre. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Un carreau de torchon reste un peu humide. Aniss pose un doigt sur le robinet. Il bouge, tout petit. Un rai de soleil barre encore l'évier.</t>
+          <t>Les mains d'Aniss laissent le bleu au fond du bac. C'était plus facile, là. Tes bras ont guidé le galet. Le fond gardera son ombre. Un carreau de torchon reste un peu humide. Aniss pose un doigt sur le verre. Une bulle bouge, toute petite. Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -15049,14 +15049,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|Les mains d'Aniss laissent le bleu descendre.
+          <t>narrateur|Les mains d'Aniss laissent le bleu au fond du bac.
 copine|C'était plus facile, là.
 papa|Tes bras ont guidé le galet.
 maman|Le fond gardera son ombre.
 narrateur|Un carreau de torchon reste un peu humide.
-narrateur|Aniss pose un doigt sur le robinet.
-narrateur|Il bouge, tout petit.
-narrateur|Un rai de soleil barre encore l'évier.</t>
+narrateur|Aniss pose un doigt sur le verre.
+narrateur|Une bulle bouge, toute petite.
+narrateur|Un rai de soleil barre encore le bac.</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16539,6 +16539,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
